--- a/masterCustomerElite.xlsx
+++ b/masterCustomerElite.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC20F2F-D87D-4FA6-975D-7BA8D3D6E897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B8F115-D0D0-4828-8EAF-9B8DA24A8396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F0871113-CB42-400C-AF82-F39C18294D72}"/>
   </bookViews>
@@ -5548,7 +5548,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -5585,9 +5585,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -31121,10 +31118,10 @@
       <c r="C965" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="D965" s="13" t="s">
+      <c r="D965" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E965" s="13" t="s">
+      <c r="E965" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F965" s="4" t="s">
@@ -31147,10 +31144,10 @@
       <c r="C966" s="6" t="s">
         <v>752</v>
       </c>
-      <c r="D966" s="13" t="s">
+      <c r="D966" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E966" s="13" t="s">
+      <c r="E966" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F966" s="4" t="s">
@@ -31173,10 +31170,10 @@
       <c r="C967" s="6" t="s">
         <v>753</v>
       </c>
-      <c r="D967" s="13" t="s">
+      <c r="D967" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E967" s="13" t="s">
+      <c r="E967" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F967" s="4" t="s">
@@ -31199,10 +31196,10 @@
       <c r="C968" s="6" t="s">
         <v>754</v>
       </c>
-      <c r="D968" s="13" t="s">
+      <c r="D968" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E968" s="13" t="s">
+      <c r="E968" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F968" s="4" t="s">
@@ -31225,10 +31222,10 @@
       <c r="C969" s="6" t="s">
         <v>755</v>
       </c>
-      <c r="D969" s="13" t="s">
+      <c r="D969" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E969" s="13" t="s">
+      <c r="E969" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F969" s="4" t="s">
@@ -31251,10 +31248,10 @@
       <c r="C970" s="6" t="s">
         <v>756</v>
       </c>
-      <c r="D970" s="13" t="s">
+      <c r="D970" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E970" s="13" t="s">
+      <c r="E970" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F970" s="4" t="s">
@@ -31277,10 +31274,10 @@
       <c r="C971" s="6" t="s">
         <v>757</v>
       </c>
-      <c r="D971" s="13" t="s">
+      <c r="D971" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E971" s="13" t="s">
+      <c r="E971" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F971" s="4" t="s">
@@ -31303,10 +31300,10 @@
       <c r="C972" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="D972" s="13" t="s">
+      <c r="D972" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E972" s="13" t="s">
+      <c r="E972" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F972" s="4" t="s">
@@ -31329,10 +31326,10 @@
       <c r="C973" s="6" t="s">
         <v>758</v>
       </c>
-      <c r="D973" s="13" t="s">
+      <c r="D973" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E973" s="13" t="s">
+      <c r="E973" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F973" s="4" t="s">
@@ -31355,10 +31352,10 @@
       <c r="C974" s="6" t="s">
         <v>759</v>
       </c>
-      <c r="D974" s="13" t="s">
+      <c r="D974" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E974" s="13" t="s">
+      <c r="E974" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F974" s="4" t="s">
@@ -31381,10 +31378,10 @@
       <c r="C975" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D975" s="13" t="s">
+      <c r="D975" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E975" s="13" t="s">
+      <c r="E975" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F975" s="4" t="s">
@@ -31407,10 +31404,10 @@
       <c r="C976" s="6" t="s">
         <v>760</v>
       </c>
-      <c r="D976" s="13" t="s">
+      <c r="D976" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E976" s="13" t="s">
+      <c r="E976" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F976" s="4" t="s">
@@ -31433,10 +31430,10 @@
       <c r="C977" s="6" t="s">
         <v>761</v>
       </c>
-      <c r="D977" s="13" t="s">
+      <c r="D977" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E977" s="13" t="s">
+      <c r="E977" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F977" s="4" t="s">
@@ -31459,10 +31456,10 @@
       <c r="C978" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D978" s="13" t="s">
+      <c r="D978" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E978" s="13" t="s">
+      <c r="E978" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F978" s="4" t="s">
@@ -31485,10 +31482,10 @@
       <c r="C979" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D979" s="13" t="s">
+      <c r="D979" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E979" s="13" t="s">
+      <c r="E979" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F979" s="4" t="s">
@@ -31511,10 +31508,10 @@
       <c r="C980" s="6" t="s">
         <v>762</v>
       </c>
-      <c r="D980" s="13" t="s">
+      <c r="D980" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E980" s="13" t="s">
+      <c r="E980" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F980" s="4" t="s">
@@ -31537,10 +31534,10 @@
       <c r="C981" s="6" t="s">
         <v>724</v>
       </c>
-      <c r="D981" s="13" t="s">
+      <c r="D981" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E981" s="13" t="s">
+      <c r="E981" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F981" s="4" t="s">
@@ -31563,10 +31560,10 @@
       <c r="C982" s="6" t="s">
         <v>763</v>
       </c>
-      <c r="D982" s="13" t="s">
+      <c r="D982" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E982" s="13" t="s">
+      <c r="E982" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F982" s="4" t="s">
@@ -31589,10 +31586,10 @@
       <c r="C983" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D983" s="13" t="s">
+      <c r="D983" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E983" s="13" t="s">
+      <c r="E983" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F983" s="4" t="s">
@@ -31615,10 +31612,10 @@
       <c r="C984" s="6" t="s">
         <v>764</v>
       </c>
-      <c r="D984" s="13" t="s">
+      <c r="D984" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="E984" s="13" t="s">
+      <c r="E984" s="6" t="s">
         <v>838</v>
       </c>
       <c r="F984" s="4" t="s">
@@ -46825,27 +46822,27 @@
       </c>
     </row>
     <row r="1570" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1570" s="14" t="s">
-        <v>1805</v>
-      </c>
-      <c r="B1570" s="14"/>
-      <c r="C1570" s="15" t="s">
+      <c r="A1570" s="13" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1570" s="13"/>
+      <c r="C1570" s="14" t="s">
         <v>1351</v>
       </c>
-      <c r="D1570" s="16" t="s">
+      <c r="D1570" s="15" t="s">
         <v>1481</v>
       </c>
-      <c r="E1570" s="16" t="s">
+      <c r="E1570" s="15" t="s">
         <v>1487</v>
       </c>
-      <c r="F1570" s="14" t="s">
-        <v>1804</v>
-      </c>
-      <c r="G1570" s="14"/>
-      <c r="H1570" s="14"/>
-      <c r="I1570" s="14"/>
-      <c r="J1570" s="14"/>
-      <c r="K1570" s="14" t="s">
+      <c r="F1570" s="13" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G1570" s="13"/>
+      <c r="H1570" s="13"/>
+      <c r="I1570" s="13"/>
+      <c r="J1570" s="13"/>
+      <c r="K1570" s="13" t="s">
         <v>1664</v>
       </c>
       <c r="L1570" s="7">
